--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2021_tarapaca.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:31</t>
+    <t xml:space="preserve">2026-09-24 01:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -712,13 +712,13 @@
         <v>6</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="11">
@@ -735,13 +735,13 @@
         <v>6</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="12">
@@ -758,13 +758,13 @@
         <v>6</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="13">
@@ -781,13 +781,13 @@
         <v>6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -827,13 +827,13 @@
         <v>6</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.41</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="16">
@@ -850,13 +850,13 @@
         <v>6</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.66</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="17">
@@ -876,10 +876,10 @@
         <v>-0.03</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="18">
